--- a/assets/infobasica/planilhas/aula21_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula21_nivel2.xlsx
@@ -904,7 +904,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Queda livre: tempo de 0 a 3 s (passo 0,1) em A2:A32 e =9,81A2^2/2, gráfico de dispersão com título e rótulos dos eixos.</t>
+          <t>Queda livre: tempo de 0 a 3 s (passo 0,1) em A2:A32 e =9,81*A2^2/2, gráfico de dispersão com título e rótulos dos eixos.</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
